--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -4917,7 +4917,7 @@
         <v>117641945</v>
       </c>
       <c r="B36" t="n">
-        <v>57534</v>
+        <v>57535</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5165,6 +5165,259 @@
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122425605</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58019</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tiberget, Venjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>436163</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6764668</v>
+      </c>
+      <c r="S38" t="n">
+        <v>69</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>David Hammarberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>David Hammarberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122425593</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Tiberget, Venjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>436163</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6764668</v>
+      </c>
+      <c r="S39" t="n">
+        <v>69</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Inflygande. Landar dolt och hörs sen söka föda. Även en kort trumning.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>David Hammarberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>David Hammarberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -5167,10 +5167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122425605</v>
+        <v>122425593</v>
       </c>
       <c r="B38" t="n">
-        <v>58019</v>
+        <v>57374</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5179,20 +5179,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103042</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5209,7 +5209,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5265,6 +5265,11 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Inflygande. Landar dolt och hörs sen söka föda. Även en kort trumning.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5291,10 +5296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122425593</v>
+        <v>122425605</v>
       </c>
       <c r="B39" t="n">
-        <v>57374</v>
+        <v>58019</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5303,20 +5308,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>103042</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5333,7 +5338,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5389,11 +5394,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Inflygande. Landar dolt och hörs sen söka föda. Även en kort trumning.</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -4036,11 +4036,11 @@
         <v>116770950</v>
       </c>
       <c r="B29" t="n">
-        <v>57369</v>
+        <v>57474</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5170,7 +5170,7 @@
         <v>122425593</v>
       </c>
       <c r="B38" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>122425605</v>
       </c>
       <c r="B39" t="n">
-        <v>58019</v>
+        <v>58024</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -4051,11 +4051,6 @@
       <c r="E29" t="n">
         <v>102626</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Törnskata</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>Lanius collurio</t>
@@ -5167,10 +5162,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122425593</v>
+        <v>122425605</v>
       </c>
       <c r="B38" t="n">
-        <v>57379</v>
+        <v>58024</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5179,20 +5174,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>103042</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5209,7 +5199,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5265,11 +5255,6 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Inflygande. Landar dolt och hörs sen söka föda. Även en kort trumning.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5296,10 +5281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122425605</v>
+        <v>122425593</v>
       </c>
       <c r="B39" t="n">
-        <v>58024</v>
+        <v>57379</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5308,20 +5293,15 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103042</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Grönfink</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5338,7 +5318,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5394,6 +5374,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Inflygande. Landar dolt och hörs sen söka föda. Även en kort trumning.</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -4036,7 +4036,7 @@
         <v>116770950</v>
       </c>
       <c r="B29" t="n">
-        <v>57474</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4050,6 +4050,11 @@
       </c>
       <c r="E29" t="n">
         <v>102626</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -5165,7 +5170,7 @@
         <v>122425605</v>
       </c>
       <c r="B38" t="n">
-        <v>58024</v>
+        <v>58028</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5179,6 +5184,11 @@
       </c>
       <c r="E38" t="n">
         <v>103042</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -5284,7 +5294,7 @@
         <v>122425593</v>
       </c>
       <c r="B39" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5298,6 +5308,11 @@
       </c>
       <c r="E39" t="n">
         <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -5167,10 +5167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122425605</v>
+        <v>122425593</v>
       </c>
       <c r="B38" t="n">
-        <v>58028</v>
+        <v>57383</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5179,20 +5179,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103042</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5209,7 +5209,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5265,6 +5265,11 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Inflygande. Landar dolt och hörs sen söka föda. Även en kort trumning.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5291,10 +5296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122425593</v>
+        <v>122425605</v>
       </c>
       <c r="B39" t="n">
-        <v>57383</v>
+        <v>58028</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5303,20 +5308,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>103042</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5333,7 +5338,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5389,11 +5394,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Inflygande. Landar dolt och hörs sen söka föda. Även en kort trumning.</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -4036,7 +4036,7 @@
         <v>116770950</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57479</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>122425593</v>
       </c>
       <c r="B38" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>122425605</v>
       </c>
       <c r="B39" t="n">
-        <v>58028</v>
+        <v>58029</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -5167,10 +5167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122425593</v>
+        <v>122425605</v>
       </c>
       <c r="B38" t="n">
-        <v>57384</v>
+        <v>58029</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5179,20 +5179,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103042</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5209,7 +5209,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5265,11 +5265,6 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Inflygande. Landar dolt och hörs sen söka föda. Även en kort trumning.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5296,10 +5291,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122425605</v>
+        <v>122425593</v>
       </c>
       <c r="B39" t="n">
-        <v>58029</v>
+        <v>57384</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5308,20 +5303,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103042</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5338,7 +5333,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5394,6 +5389,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Inflygande. Landar dolt och hörs sen söka föda. Även en kort trumning.</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -5294,7 +5294,7 @@
         <v>122425593</v>
       </c>
       <c r="B39" t="n">
-        <v>57384</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5418,6 +5418,139 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>123215758</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57484</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Tiberget, Venjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>436163</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6764668</v>
+      </c>
+      <c r="S40" t="n">
+        <v>69</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Småtrummar under födosök.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>David Hammarberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>David Hammarberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -5294,7 +5294,7 @@
         <v>122425593</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>123215758</v>
       </c>
       <c r="B40" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -3414,7 +3414,7 @@
         <v>39452309</v>
       </c>
       <c r="B24" t="n">
-        <v>57262</v>
+        <v>57484</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>123215758</v>
       </c>
       <c r="B40" t="n">
-        <v>57487</v>
+        <v>57493</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -3414,7 +3414,7 @@
         <v>39452309</v>
       </c>
       <c r="B24" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>123215758</v>
       </c>
       <c r="B40" t="n">
-        <v>57493</v>
+        <v>57496</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3414,7 +3414,7 @@
         <v>39452309</v>
       </c>
       <c r="B24" t="n">
-        <v>57487</v>
+        <v>57488</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3532,10 +3532,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113883404</v>
+        <v>116770945</v>
       </c>
       <c r="B25" t="n">
-        <v>57414</v>
+        <v>56624</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3544,37 +3544,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100065</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3614,27 +3614,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-01-04</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-01-04</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Matning.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3654,44 +3649,44 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tobias Hammarberg</t>
+          <t>Tobias Hammarberg, David Hammarberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>116770946</v>
+        <v>116770950</v>
       </c>
       <c r="B26" t="n">
-        <v>56710</v>
+        <v>57573</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100091</v>
+        <v>102626</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3699,8 +3694,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -3759,6 +3762,11 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Vid risupplag efter avverkning.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3785,10 +3793,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>116770962</v>
+        <v>116770965</v>
       </c>
       <c r="B27" t="n">
-        <v>57699</v>
+        <v>57805</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3797,30 +3805,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102999</v>
+        <v>102990</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3909,10 +3917,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>116770945</v>
+        <v>116770955</v>
       </c>
       <c r="B28" t="n">
-        <v>56624</v>
+        <v>57637</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3925,16 +3933,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100065</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3951,7 +3959,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4026,21 +4034,21 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tobias Hammarberg, David Hammarberg</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>116770950</v>
+        <v>116770972</v>
       </c>
       <c r="B29" t="n">
-        <v>57573</v>
+        <v>57929</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4049,41 +4057,33 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102626</v>
+        <v>103044</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4139,11 +4139,6 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Vid risupplag efter avverkning.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4170,10 +4165,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>116770964</v>
+        <v>121879727</v>
       </c>
       <c r="B30" t="n">
-        <v>57747</v>
+        <v>56587</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4182,37 +4177,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103018</v>
+        <v>102613</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4252,22 +4247,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>20-25 st. Stöts när jag rullar in i fäboden.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4287,17 +4287,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tobias Hammarberg, David Hammarberg</t>
+          <t>Tobias Hammarberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>116770949</v>
+        <v>122425593</v>
       </c>
       <c r="B31" t="n">
-        <v>57294</v>
+        <v>57481</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4310,16 +4310,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4336,7 +4336,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4376,22 +4376,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Inflygande. Landar dolt och hörs sen söka föda. Även en kort trumning.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4406,22 +4411,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tobias Hammarberg</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tobias Hammarberg, David Hammarberg</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>116770965</v>
+        <v>123215758</v>
       </c>
       <c r="B32" t="n">
-        <v>57805</v>
+        <v>57497</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4430,20 +4435,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102990</v>
+        <v>100048</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4453,14 +4458,18 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4500,22 +4509,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Småtrummar under födosök.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4530,1026 +4544,15 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tobias Hammarberg</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tobias Hammarberg, David Hammarberg</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>116770955</v>
-      </c>
-      <c r="B33" t="n">
-        <v>57637</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Regulus regulus</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Tiberget, Venjan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>436163</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6764668</v>
-      </c>
-      <c r="S33" t="n">
-        <v>69</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Vänjan</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>08:58</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Tobias Hammarberg</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>David Hammarberg</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>116770959</v>
-      </c>
-      <c r="B34" t="n">
-        <v>57693</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>103001</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Turdus iliacus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Tiberget, Venjan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>436163</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6764668</v>
-      </c>
-      <c r="S34" t="n">
-        <v>69</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Vänjan</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>08:58</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Tobias Hammarberg</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Tobias Hammarberg, David Hammarberg</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>116770972</v>
-      </c>
-      <c r="B35" t="n">
-        <v>57929</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>103044</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Grönsiska</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Spinus spinus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Tiberget, Venjan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>436163</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6764668</v>
-      </c>
-      <c r="S35" t="n">
-        <v>69</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Vänjan</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>08:58</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Tobias Hammarberg</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Tobias Hammarberg, David Hammarberg</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>117641945</v>
-      </c>
-      <c r="B36" t="n">
-        <v>57535</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>103012</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Grönsångare</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Phylloscopus sibilatrix</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Tiberget, Venjan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>436163</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6764668</v>
-      </c>
-      <c r="S36" t="n">
-        <v>69</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Vänjan</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>David Hammarberg</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>David Hammarberg</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>121879727</v>
-      </c>
-      <c r="B37" t="n">
-        <v>56587</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>102613</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Orre</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Lyrurus tetrix</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Tiberget, Venjan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>436163</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6764668</v>
-      </c>
-      <c r="S37" t="n">
-        <v>69</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Vänjan</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2025-01-03</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2025-01-03</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>20-25 st. Stöts när jag rullar in i fäboden.</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Tobias Hammarberg</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Tobias Hammarberg</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>122425605</v>
-      </c>
-      <c r="B38" t="n">
-        <v>58123</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>103042</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Grönfink</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Chloris chloris</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Tiberget, Venjan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>436163</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6764668</v>
-      </c>
-      <c r="S38" t="n">
-        <v>69</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Vänjan</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>David Hammarberg</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>David Hammarberg</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>122425593</v>
-      </c>
-      <c r="B39" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Tiberget, Venjan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>436163</v>
-      </c>
-      <c r="R39" t="n">
-        <v>6764668</v>
-      </c>
-      <c r="S39" t="n">
-        <v>69</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Vänjan</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Inflygande. Landar dolt och hörs sen söka föda. Även en kort trumning.</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>David Hammarberg</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>David Hammarberg</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>123215758</v>
-      </c>
-      <c r="B40" t="n">
-        <v>57496</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>100048</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Dryobates minor</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Tiberget, Venjan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>436163</v>
-      </c>
-      <c r="R40" t="n">
-        <v>6764668</v>
-      </c>
-      <c r="S40" t="n">
-        <v>69</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Vänjan</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>08:25</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Småtrummar under födosök.</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>David Hammarberg</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>David Hammarberg</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4554,6 +4554,130 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125491436</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57918</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tiberget, Venjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>436163</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6764668</v>
+      </c>
+      <c r="S33" t="n">
+        <v>69</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>David Hammarberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>David Hammarberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -4559,7 +4559,7 @@
         <v>125491436</v>
       </c>
       <c r="B33" t="n">
-        <v>57918</v>
+        <v>58026</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -4559,12 +4559,7 @@
         <v>125491436</v>
       </c>
       <c r="B33" t="n">
-        <v>58026</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -4559,7 +4559,7 @@
         <v>125491436</v>
       </c>
       <c r="B33" t="n">
-        <v>58044</v>
+        <v>58045</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 50690-2020 artfynd.xlsx
+++ b/artfynd/A 50690-2020 artfynd.xlsx
@@ -4559,7 +4559,7 @@
         <v>125491436</v>
       </c>
       <c r="B33" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
